--- a/temp_Copie de BD_transparence.xlsx
+++ b/temp_Copie de BD_transparence.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alila\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5446DC4-9AF8-437E-B901-11D11B327A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AB0FEC-0FC0-4E70-B046-ECC6A4878E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="BD" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BD!$A$1:$O$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BD!$A$1:$O$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="179">
   <si>
     <t>Produit</t>
   </si>
@@ -167,9 +167,6 @@
     <t>9.3 g</t>
   </si>
   <si>
-    <t>7.4 g</t>
-  </si>
-  <si>
     <t>https://fr.openfoodfacts.org/produit/3564700596968/pain-de-mie-grandes-tranches-complet-marque-repere</t>
   </si>
   <si>
@@ -185,51 +182,12 @@
     <t>https://fr.openfoodfacts.org/produit/8710637105352/wraps-au-ble-nature-mission</t>
   </si>
   <si>
-    <t>Maïs doux – Mido – 150g (140g égoutté)</t>
-  </si>
-  <si>
-    <t>0.4 g</t>
-  </si>
-  <si>
     <t>6.7 g</t>
   </si>
   <si>
     <t>2.5 g</t>
   </si>
   <si>
-    <t>https://fr.openfoodfacts.org/produit/6111069000499/mais-doux-mido</t>
-  </si>
-  <si>
-    <t>Maïs Doux –</t>
-  </si>
-  <si>
-    <t>https://fr.openfoodfacts.org/produit/6111250470810/mais-doux</t>
-  </si>
-  <si>
-    <t>0.2 g</t>
-  </si>
-  <si>
-    <t>5.5 g</t>
-  </si>
-  <si>
-    <t>3.2 g</t>
-  </si>
-  <si>
-    <t>Ramen soja caramel – Tanoshi – 360 g</t>
-  </si>
-  <si>
-    <t>0.1 g</t>
-  </si>
-  <si>
-    <t>5.3 g</t>
-  </si>
-  <si>
-    <t>1.7 g</t>
-  </si>
-  <si>
-    <t>https://fr.openfoodfacts.org/produit/3229820181363/ramen-soja-caramel-tanoshi</t>
-  </si>
-  <si>
     <t>Mature Cheddar &amp; Chive – Tyrell's – 150 g</t>
   </si>
   <si>
@@ -311,18 +269,6 @@
     <t>https://fr.openfoodfacts.org/produit/3564707001236/galettes-riz-complet-bio-village</t>
   </si>
   <si>
-    <t>Céréales de campagne – Tipiak – 330 g (2 x 165 g)</t>
-  </si>
-  <si>
-    <t>3.5 g</t>
-  </si>
-  <si>
-    <t>4.8 g</t>
-  </si>
-  <si>
-    <t>https://fr.openfoodfacts.org/produit/3600900020091/cereales-de-campagne-tipiak</t>
-  </si>
-  <si>
     <t>Galettes Riz complet – Carrefour BIO – 130 g</t>
   </si>
   <si>
@@ -356,15 +302,6 @@
     <t>https://fr.openfoodfacts.org/produit/3564707082310/galettes-4-cereales-bio-bio-village</t>
   </si>
   <si>
-    <t>Céréales Granola fruits rouges 350g – U – 350 g</t>
-  </si>
-  <si>
-    <t>17 g</t>
-  </si>
-  <si>
-    <t>https://fr.openfoodfacts.org/produit/3256229255623/cereales-granola-fruits-rouges-350g-u</t>
-  </si>
-  <si>
     <t>Céréales Extra Pépites Chocolat Noisettes – Kellogg's – 500 g</t>
   </si>
   <si>
@@ -416,9 +353,6 @@
     <t>https://fr.openfoodfacts.org/produit/3564700098905/pate-feuilletee-pur-beurre-marque-repere</t>
   </si>
   <si>
-    <t>4 mg</t>
-  </si>
-  <si>
     <t>6,3 g</t>
   </si>
   <si>
@@ -461,24 +395,6 @@
     <t>392 mg</t>
   </si>
   <si>
-    <t>343 kj</t>
-  </si>
-  <si>
-    <t>200 mg</t>
-  </si>
-  <si>
-    <t>289 kj</t>
-  </si>
-  <si>
-    <t>120 mg</t>
-  </si>
-  <si>
-    <t>692 kj</t>
-  </si>
-  <si>
-    <t>600 mg</t>
-  </si>
-  <si>
     <t>2113 kj</t>
   </si>
   <si>
@@ -509,9 +425,6 @@
     <t>1670 kj</t>
   </si>
   <si>
-    <t>1456 kj</t>
-  </si>
-  <si>
     <t>1644 kj</t>
   </si>
   <si>
@@ -527,9 +440,6 @@
     <t>87,2 mg</t>
   </si>
   <si>
-    <t xml:space="preserve">1771 kj </t>
-  </si>
-  <si>
     <t>2076 kj</t>
   </si>
   <si>
@@ -579,6 +489,90 @@
   </si>
   <si>
     <t>0 g</t>
+  </si>
+  <si>
+    <t>Organic Lightly Salted Wholegrain Low Fat Rice Cakes – Kallo – 130 g</t>
+  </si>
+  <si>
+    <t>1648 kj</t>
+  </si>
+  <si>
+    <t>118 mg</t>
+  </si>
+  <si>
+    <t>8.5 g</t>
+  </si>
+  <si>
+    <t>https://world.openfoodfacts.org/product/5013665100065/organic-lightly-salted-wholegrain-low-fat-rice-cakes-kallo</t>
+  </si>
+  <si>
+    <t>Pepsil – Lidl – 750 g</t>
+  </si>
+  <si>
+    <t>1089 kj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 g </t>
+  </si>
+  <si>
+    <t>4.5 %</t>
+  </si>
+  <si>
+    <t>https://world.openfoodfacts.org/product/4056489007180/pepsil-lidl</t>
+  </si>
+  <si>
+    <t>Muesli – Alpen – 550g</t>
+  </si>
+  <si>
+    <t>1548 kj</t>
+  </si>
+  <si>
+    <t>18 g</t>
+  </si>
+  <si>
+    <t>110 mg</t>
+  </si>
+  <si>
+    <t>https://world.openfoodfacts.org/product/5010029226188/muesli-alpen</t>
+  </si>
+  <si>
+    <t>Pain de mie american sandwich complet sans sucres ajoutés 600g – Harrys – 600 g</t>
+  </si>
+  <si>
+    <t>1178 kj</t>
+  </si>
+  <si>
+    <t>7.7 g</t>
+  </si>
+  <si>
+    <t>8.1 g</t>
+  </si>
+  <si>
+    <t>2.745 %</t>
+  </si>
+  <si>
+    <t>https://world.openfoodfacts.org/product/3228857002344/pain-de-mie-american-sandwich-complet-sans-sucres-ajoutes-600g-harrys</t>
+  </si>
+  <si>
+    <t>Simply Delicious Muesli – Dorset Cereals – 650g</t>
+  </si>
+  <si>
+    <t>1540 kj</t>
+  </si>
+  <si>
+    <t>14.7 g</t>
+  </si>
+  <si>
+    <t>12 mg</t>
+  </si>
+  <si>
+    <t>9.6 g</t>
+  </si>
+  <si>
+    <t>9 g</t>
+  </si>
+  <si>
+    <t>https://world.openfoodfacts.org/product/5018357012411/simply-delicious-muesli-dorset-cereals</t>
   </si>
 </sst>
 </file>
@@ -635,7 +629,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -658,12 +652,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -682,6 +687,19 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1013,25 +1031,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -1060,7 +1078,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>15</v>
@@ -1069,7 +1087,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>17</v>
@@ -1107,7 +1125,7 @@
         <v>20</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>21</v>
@@ -1116,13 +1134,13 @@
         <v>22</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="H3" s="7">
         <v>4.4999999999999998E-2</v>
@@ -1154,7 +1172,7 @@
         <v>28</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>29</v>
@@ -1163,7 +1181,7 @@
         <v>30</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>31</v>
@@ -1201,7 +1219,7 @@
         <v>33</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>34</v>
@@ -1210,13 +1228,13 @@
         <v>35</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="H5" s="9">
         <v>0</v>
@@ -1248,7 +1266,7 @@
         <v>39</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>40</v>
@@ -1257,13 +1275,13 @@
         <v>41</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="H6" s="7">
         <v>1.418E-2</v>
@@ -1287,30 +1305,30 @@
         <v>2</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="H7" s="9">
         <v>0</v>
@@ -1334,36 +1352,36 @@
         <v>4</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>180</v>
+      <c r="G8" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="H8" s="7">
-        <v>0.83313999999999999</v>
+        <v>1.92E-3</v>
       </c>
       <c r="I8" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>12</v>
@@ -1372,24 +1390,24 @@
         <v>12</v>
       </c>
       <c r="L8" s="5">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="N8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>56</v>
@@ -1398,19 +1416,19 @@
         <v>57</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>180</v>
+      <c r="G9" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="H9" s="7">
-        <v>0.85616000000000003</v>
+        <v>9.7500000000000003E-2</v>
       </c>
       <c r="I9" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>12</v>
@@ -1419,45 +1437,45 @@
         <v>12</v>
       </c>
       <c r="L9" s="5">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>9</v>
       </c>
       <c r="N9" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="2" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H10" s="7">
-        <v>2.1800000000000001E-3</v>
+      <c r="H10" s="9">
+        <v>0</v>
       </c>
       <c r="I10" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>12</v>
@@ -1466,13 +1484,13 @@
         <v>12</v>
       </c>
       <c r="L10" s="5">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>9</v>
       </c>
       <c r="N10" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>63</v>
@@ -1483,25 +1501,25 @@
         <v>64</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H11" s="7">
-        <v>1.92E-3</v>
+        <v>48</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0</v>
       </c>
       <c r="I11" s="5">
         <v>1</v>
@@ -1513,7 +1531,7 @@
         <v>12</v>
       </c>
       <c r="L11" s="5">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>9</v>
@@ -1522,36 +1540,36 @@
         <v>1</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H12" s="7">
-        <v>9.7500000000000003E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="I12" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>12</v>
@@ -1560,7 +1578,7 @@
         <v>12</v>
       </c>
       <c r="L12" s="5">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>9</v>
@@ -1569,36 +1587,36 @@
         <v>3</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="2" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="H13" s="9">
         <v>0</v>
       </c>
       <c r="I13" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>12</v>
@@ -1607,39 +1625,39 @@
         <v>12</v>
       </c>
       <c r="L13" s="5">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N13" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="E14" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="H14" s="9">
         <v>0</v>
@@ -1654,13 +1672,13 @@
         <v>12</v>
       </c>
       <c r="L14" s="5">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>81</v>
@@ -1671,25 +1689,25 @@
         <v>82</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H15" s="7">
-        <v>3.6999999999999998E-2</v>
+      <c r="H15" s="9">
+        <v>0</v>
       </c>
       <c r="I15" s="5">
         <v>1</v>
@@ -1701,39 +1719,39 @@
         <v>12</v>
       </c>
       <c r="L15" s="5">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N15" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="H16" s="9">
         <v>0</v>
@@ -1757,481 +1775,481 @@
         <v>0</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="H17" s="9">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I17" s="5">
-        <v>-4</v>
+        <v>22</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L17" s="5">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>9</v>
       </c>
       <c r="N17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H18" s="7">
+        <v>2.6349999999999998E-2</v>
+      </c>
+      <c r="I18" s="5">
+        <v>19</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L18" s="5">
+        <v>20</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N18" s="3">
+        <v>7</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="H18" s="9">
-        <v>0</v>
-      </c>
-      <c r="I18" s="5">
-        <v>1</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L18" s="5">
-        <v>69</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H19" s="9">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I19" s="5">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L19" s="5">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N19" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0.08</v>
+      </c>
+      <c r="I20" s="5">
+        <v>22</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L20" s="5">
+        <v>20</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N20" s="3">
+        <v>2</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H20" s="9">
-        <v>0</v>
-      </c>
-      <c r="I20" s="5">
-        <v>2</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L20" s="5">
-        <v>69</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="7">
-        <v>5.2659999999999998E-2</v>
+        <v>65</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0</v>
       </c>
       <c r="I21" s="5">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L21" s="5">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>9</v>
       </c>
       <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" t="s">
+        <v>151</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="H22" s="13">
+        <v>0</v>
+      </c>
+      <c r="I22" s="12">
         <v>2</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="J22" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L22" s="12">
+        <v>69</v>
+      </c>
+      <c r="M22" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="N22" s="10">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" t="s">
+        <v>156</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23" s="12">
+        <v>2</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L23" s="14">
+        <v>74</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="N23" s="10">
+        <v>1</v>
+      </c>
+      <c r="O23" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="F24" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="G24" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="I24" s="12">
+        <v>1</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L24" s="12">
+        <v>67</v>
+      </c>
+      <c r="M24" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="N24" s="10">
+        <v>0</v>
+      </c>
+      <c r="O24" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="9">
-        <v>0.03</v>
-      </c>
-      <c r="I22" s="5">
-        <v>22</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L22" s="5">
-        <v>15</v>
-      </c>
-      <c r="M22" s="3" t="s">
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" t="s">
+        <v>166</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="I25" s="12">
+        <v>1</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L25" s="12">
+        <v>74</v>
+      </c>
+      <c r="M25" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N25" s="10">
         <v>1</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H23" s="7">
-        <v>2.6349999999999998E-2</v>
-      </c>
-      <c r="I23" s="5">
-        <v>19</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L23" s="5">
-        <v>20</v>
-      </c>
-      <c r="M23" s="3" t="s">
+      <c r="O25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" t="s">
+        <v>172</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H26" s="13">
+        <v>0.22</v>
+      </c>
+      <c r="I26" s="12">
+        <v>1</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L26" s="12">
+        <v>62</v>
+      </c>
+      <c r="M26" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="N23" s="3">
-        <v>7</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H24" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="I24" s="5">
-        <v>23</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L24" s="5">
-        <v>25</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N24" s="3">
-        <v>2</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H25" s="9">
-        <v>0.08</v>
-      </c>
-      <c r="I25" s="5">
-        <v>22</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L25" s="5">
-        <v>20</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N25" s="3">
-        <v>2</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H26" s="4">
+      <c r="N26" s="10">
         <v>0</v>
       </c>
-      <c r="I26" s="5">
-        <v>19</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L26" s="5">
-        <v>69</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>125</v>
+      <c r="O26" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O26" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:O21" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="O7" r:id="rId1" xr:uid="{133C2939-3246-4ED8-9749-819AC0564BC8}"/>
